--- a/simulations/AON_88/mass_flow_data_AON_88.xlsx
+++ b/simulations/AON_88/mass_flow_data_AON_88.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AON_88\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1CA7A6-2718-44F8-A36A-313F8B12E47F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D38EAC-07C7-4BBC-8A85-754F0D5A8E7D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -807,7 +807,7 @@
       </c>
       <c r="E4" s="5">
         <f t="shared" ref="E4:E12" si="0">D4/$D$12</f>
-        <v>1.7279385507269518</v>
+        <v>1.7279423803507969</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
@@ -825,7 +825,7 @@
       </c>
       <c r="E5" s="5">
         <f t="shared" si="0"/>
-        <v>0.91964998512365381</v>
+        <v>0.91965202334052831</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -861,11 +861,11 @@
       </c>
       <c r="E7" s="5">
         <f t="shared" si="0"/>
-        <v>1.5135368309933237</v>
+        <v>1.513540185439427</v>
       </c>
       <c r="F7" s="18">
         <f>E7/1000</f>
-        <v>1.5135368309933236E-3</v>
+        <v>1.5135401854394271E-3</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -883,7 +883,7 @@
       </c>
       <c r="E8" s="5">
         <f t="shared" si="0"/>
-        <v>7.842128857001375E-2</v>
+        <v>7.842146237482675E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -901,7 +901,7 @@
       </c>
       <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>1.4556189599066783E-2</v>
+        <v>1.4556221859896173E-2</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="E10" s="5">
         <f t="shared" si="0"/>
-        <v>2.0022743606470884E-4</v>
+        <v>2.0022787982803785E-4</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="E11" s="5">
         <f t="shared" si="0"/>
-        <v>4.0876037468980504E-2</v>
+        <v>4.0876128062391784E-2</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -963,7 +963,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="4">
-        <v>37500.010392935503</v>
+        <v>37499.927281984797</v>
       </c>
       <c r="E12" s="5">
         <f t="shared" si="0"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="D3" s="5">
         <f>C3/'Material streams'!$D$12</f>
-        <v>4.4085295781983044E-2</v>
+        <v>4.4085393488061703E-2</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D4" s="5">
         <f>C4/'Material streams'!$D$12</f>
-        <v>1.6668717940349055E-2</v>
+        <v>1.6668754883167228E-2</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D5" s="16">
         <f>SUM(D3:D4)</f>
-        <v>6.0754013722332099E-2</v>
+        <v>6.075414837122893E-2</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
@@ -1651,11 +1651,11 @@
       </c>
       <c r="D2" s="4">
         <f>C2/'Material streams'!$D$12</f>
-        <v>242.78851515401405</v>
+        <v>242.78905324530589</v>
       </c>
       <c r="E2" s="19">
         <f>B2/1000/'Material streams'!$D$12</f>
-        <v>0.50722214107282404</v>
+        <v>0.50722326522738703</v>
       </c>
       <c r="H2" s="10"/>
     </row>
@@ -1672,11 +1672,11 @@
       </c>
       <c r="D3" s="4">
         <f>C3/'Material streams'!$D$12</f>
-        <v>223.02893928682971</v>
+        <v>223.02943358504632</v>
       </c>
       <c r="E3" s="19">
         <f>B3/1000/'Material streams'!$D$12</f>
-        <v>4.6646502651840436</v>
+        <v>4.6646606034312441</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
